--- a/projects/project-3/assignment/src/data/to-axioms.xlsx
+++ b/projects/project-3/assignment/src/data/to-axioms.xlsx
@@ -463,7 +463,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>http://www.w3.org/2000/01/rdf-schema#subClassOf n31ccfe26a08a4e0998a9be49a579bbf3b5</t>
+          <t>http://www.w3.org/2000/01/rdf-schema#subClassOf n4a1b7597cfd248eb89bbac37dd02f346b5</t>
         </is>
       </c>
     </row>
@@ -480,7 +480,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>http://www.w3.org/2000/01/rdf-schema#subClassOf n31ccfe26a08a4e0998a9be49a579bbf3b6</t>
+          <t>http://www.w3.org/2000/01/rdf-schema#subClassOf n4a1b7597cfd248eb89bbac37dd02f346b6</t>
         </is>
       </c>
     </row>
@@ -514,7 +514,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>http://www.w3.org/2000/01/rdf-schema#subClassOf n31ccfe26a08a4e0998a9be49a579bbf3b1</t>
+          <t>http://www.w3.org/2000/01/rdf-schema#subClassOf n4a1b7597cfd248eb89bbac37dd02f346b1</t>
         </is>
       </c>
     </row>
@@ -531,7 +531,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>http://www.w3.org/2000/01/rdf-schema#subClassOf n31ccfe26a08a4e0998a9be49a579bbf3b2</t>
+          <t>http://www.w3.org/2000/01/rdf-schema#subClassOf n4a1b7597cfd248eb89bbac37dd02f346b2</t>
         </is>
       </c>
     </row>
@@ -548,7 +548,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>http://www.w3.org/2000/01/rdf-schema#subClassOf n31ccfe26a08a4e0998a9be49a579bbf3b3</t>
+          <t>http://www.w3.org/2000/01/rdf-schema#subClassOf n4a1b7597cfd248eb89bbac37dd02f346b3</t>
         </is>
       </c>
     </row>
@@ -565,7 +565,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>http://www.w3.org/2000/01/rdf-schema#subClassOf n31ccfe26a08a4e0998a9be49a579bbf3b4</t>
+          <t>http://www.w3.org/2000/01/rdf-schema#subClassOf n4a1b7597cfd248eb89bbac37dd02f346b4</t>
         </is>
       </c>
     </row>
@@ -633,7 +633,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>http://www.w3.org/2000/01/rdf-schema#subClassOf n31ccfe26a08a4e0998a9be49a579bbf3b7</t>
+          <t>http://www.w3.org/2000/01/rdf-schema#subClassOf n4a1b7597cfd248eb89bbac37dd02f346b7</t>
         </is>
       </c>
     </row>
@@ -650,7 +650,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>http://www.w3.org/2000/01/rdf-schema#subClassOf n31ccfe26a08a4e0998a9be49a579bbf3b8</t>
+          <t>http://www.w3.org/2000/01/rdf-schema#subClassOf n4a1b7597cfd248eb89bbac37dd02f346b8</t>
         </is>
       </c>
     </row>
@@ -667,7 +667,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>http://www.w3.org/2000/01/rdf-schema#subClassOf n31ccfe26a08a4e0998a9be49a579bbf3b9</t>
+          <t>http://www.w3.org/2000/01/rdf-schema#subClassOf n4a1b7597cfd248eb89bbac37dd02f346b9</t>
         </is>
       </c>
     </row>
@@ -684,7 +684,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>http://www.w3.org/2000/01/rdf-schema#subClassOf n31ccfe26a08a4e0998a9be49a579bbf3b10</t>
+          <t>http://www.w3.org/2000/01/rdf-schema#subClassOf n4a1b7597cfd248eb89bbac37dd02f346b10</t>
         </is>
       </c>
     </row>
@@ -701,7 +701,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>http://www.w3.org/2000/01/rdf-schema#subClassOf n31ccfe26a08a4e0998a9be49a579bbf3b11</t>
+          <t>http://www.w3.org/2000/01/rdf-schema#subClassOf n4a1b7597cfd248eb89bbac37dd02f346b11</t>
         </is>
       </c>
     </row>
@@ -718,7 +718,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>http://www.w3.org/2000/01/rdf-schema#subClassOf n31ccfe26a08a4e0998a9be49a579bbf3b12</t>
+          <t>http://www.w3.org/2000/01/rdf-schema#subClassOf n4a1b7597cfd248eb89bbac37dd02f346b12</t>
         </is>
       </c>
     </row>
@@ -735,7 +735,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>http://www.w3.org/2000/01/rdf-schema#subClassOf n31ccfe26a08a4e0998a9be49a579bbf3b13</t>
+          <t>http://www.w3.org/2000/01/rdf-schema#subClassOf n4a1b7597cfd248eb89bbac37dd02f346b13</t>
         </is>
       </c>
     </row>
@@ -752,7 +752,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>http://www.w3.org/2000/01/rdf-schema#subClassOf n31ccfe26a08a4e0998a9be49a579bbf3b14</t>
+          <t>http://www.w3.org/2000/01/rdf-schema#subClassOf n4a1b7597cfd248eb89bbac37dd02f346b14</t>
         </is>
       </c>
     </row>
@@ -786,7 +786,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>http://www.w3.org/2000/01/rdf-schema#subClassOf n31ccfe26a08a4e0998a9be49a579bbf3b15</t>
+          <t>http://www.w3.org/2000/01/rdf-schema#subClassOf n4a1b7597cfd248eb89bbac37dd02f346b15</t>
         </is>
       </c>
     </row>
@@ -803,7 +803,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>http://www.w3.org/2000/01/rdf-schema#subClassOf n31ccfe26a08a4e0998a9be49a579bbf3b16</t>
+          <t>http://www.w3.org/2000/01/rdf-schema#subClassOf n4a1b7597cfd248eb89bbac37dd02f346b16</t>
         </is>
       </c>
     </row>
@@ -820,7 +820,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>http://www.w3.org/2000/01/rdf-schema#subClassOf n31ccfe26a08a4e0998a9be49a579bbf3b17</t>
+          <t>http://www.w3.org/2000/01/rdf-schema#subClassOf n4a1b7597cfd248eb89bbac37dd02f346b17</t>
         </is>
       </c>
     </row>
@@ -837,7 +837,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>http://www.w3.org/2000/01/rdf-schema#subClassOf n31ccfe26a08a4e0998a9be49a579bbf3b18</t>
+          <t>http://www.w3.org/2000/01/rdf-schema#subClassOf n4a1b7597cfd248eb89bbac37dd02f346b18</t>
         </is>
       </c>
     </row>
@@ -854,7 +854,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>http://www.w3.org/2000/01/rdf-schema#subClassOf n31ccfe26a08a4e0998a9be49a579bbf3b19</t>
+          <t>http://www.w3.org/2000/01/rdf-schema#subClassOf n4a1b7597cfd248eb89bbac37dd02f346b19</t>
         </is>
       </c>
     </row>
@@ -871,7 +871,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>http://www.w3.org/2000/01/rdf-schema#subClassOf n31ccfe26a08a4e0998a9be49a579bbf3b20</t>
+          <t>http://www.w3.org/2000/01/rdf-schema#subClassOf n4a1b7597cfd248eb89bbac37dd02f346b20</t>
         </is>
       </c>
     </row>
@@ -888,7 +888,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>http://www.w3.org/2000/01/rdf-schema#subClassOf n31ccfe26a08a4e0998a9be49a579bbf3b21</t>
+          <t>http://www.w3.org/2000/01/rdf-schema#subClassOf n4a1b7597cfd248eb89bbac37dd02f346b21</t>
         </is>
       </c>
     </row>
@@ -905,7 +905,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>http://www.w3.org/2000/01/rdf-schema#subClassOf n31ccfe26a08a4e0998a9be49a579bbf3b22</t>
+          <t>http://www.w3.org/2000/01/rdf-schema#subClassOf n4a1b7597cfd248eb89bbac37dd02f346b22</t>
         </is>
       </c>
     </row>
@@ -922,7 +922,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>http://www.w3.org/2000/01/rdf-schema#subClassOf n31ccfe26a08a4e0998a9be49a579bbf3b23</t>
+          <t>http://www.w3.org/2000/01/rdf-schema#subClassOf n4a1b7597cfd248eb89bbac37dd02f346b23</t>
         </is>
       </c>
     </row>
@@ -939,7 +939,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>http://www.w3.org/2000/01/rdf-schema#subClassOf n31ccfe26a08a4e0998a9be49a579bbf3b24</t>
+          <t>http://www.w3.org/2000/01/rdf-schema#subClassOf n4a1b7597cfd248eb89bbac37dd02f346b24</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>http://www.w3.org/2000/01/rdf-schema#subClassOf n31ccfe26a08a4e0998a9be49a579bbf3b25</t>
+          <t>http://www.w3.org/2000/01/rdf-schema#subClassOf n4a1b7597cfd248eb89bbac37dd02f346b25</t>
         </is>
       </c>
     </row>
@@ -973,7 +973,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>http://www.w3.org/2000/01/rdf-schema#subClassOf n31ccfe26a08a4e0998a9be49a579bbf3b26</t>
+          <t>http://www.w3.org/2000/01/rdf-schema#subClassOf n4a1b7597cfd248eb89bbac37dd02f346b26</t>
         </is>
       </c>
     </row>
@@ -1007,7 +1007,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>http://www.w3.org/2000/01/rdf-schema#subClassOf n31ccfe26a08a4e0998a9be49a579bbf3b27</t>
+          <t>http://www.w3.org/2000/01/rdf-schema#subClassOf n4a1b7597cfd248eb89bbac37dd02f346b27</t>
         </is>
       </c>
     </row>
@@ -1024,7 +1024,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>http://www.w3.org/2000/01/rdf-schema#subClassOf n31ccfe26a08a4e0998a9be49a579bbf3b28</t>
+          <t>http://www.w3.org/2000/01/rdf-schema#subClassOf n4a1b7597cfd248eb89bbac37dd02f346b28</t>
         </is>
       </c>
     </row>
@@ -1041,7 +1041,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>http://www.w3.org/2000/01/rdf-schema#subClassOf n31ccfe26a08a4e0998a9be49a579bbf3b29</t>
+          <t>http://www.w3.org/2000/01/rdf-schema#subClassOf n4a1b7597cfd248eb89bbac37dd02f346b29</t>
         </is>
       </c>
     </row>
@@ -1058,7 +1058,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>http://www.w3.org/2000/01/rdf-schema#subClassOf n31ccfe26a08a4e0998a9be49a579bbf3b30</t>
+          <t>http://www.w3.org/2000/01/rdf-schema#subClassOf n4a1b7597cfd248eb89bbac37dd02f346b30</t>
         </is>
       </c>
     </row>
@@ -1075,7 +1075,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>http://www.w3.org/2000/01/rdf-schema#subClassOf n31ccfe26a08a4e0998a9be49a579bbf3b31</t>
+          <t>http://www.w3.org/2000/01/rdf-schema#subClassOf n4a1b7597cfd248eb89bbac37dd02f346b31</t>
         </is>
       </c>
     </row>
@@ -1092,7 +1092,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>http://www.w3.org/2000/01/rdf-schema#subClassOf n31ccfe26a08a4e0998a9be49a579bbf3b32</t>
+          <t>http://www.w3.org/2000/01/rdf-schema#subClassOf n4a1b7597cfd248eb89bbac37dd02f346b32</t>
         </is>
       </c>
     </row>
@@ -1109,7 +1109,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>http://www.w3.org/2000/01/rdf-schema#subClassOf n31ccfe26a08a4e0998a9be49a579bbf3b33</t>
+          <t>http://www.w3.org/2000/01/rdf-schema#subClassOf n4a1b7597cfd248eb89bbac37dd02f346b33</t>
         </is>
       </c>
     </row>
@@ -1126,7 +1126,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>http://www.w3.org/2000/01/rdf-schema#subClassOf n31ccfe26a08a4e0998a9be49a579bbf3b34</t>
+          <t>http://www.w3.org/2000/01/rdf-schema#subClassOf n4a1b7597cfd248eb89bbac37dd02f346b34</t>
         </is>
       </c>
     </row>
@@ -1160,7 +1160,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>http://www.w3.org/2000/01/rdf-schema#subClassOf n31ccfe26a08a4e0998a9be49a579bbf3b37</t>
+          <t>http://www.w3.org/2000/01/rdf-schema#subClassOf n4a1b7597cfd248eb89bbac37dd02f346b37</t>
         </is>
       </c>
     </row>
@@ -1177,7 +1177,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>http://www.w3.org/2000/01/rdf-schema#subClassOf n31ccfe26a08a4e0998a9be49a579bbf3b38</t>
+          <t>http://www.w3.org/2000/01/rdf-schema#subClassOf n4a1b7597cfd248eb89bbac37dd02f346b38</t>
         </is>
       </c>
     </row>
@@ -1194,7 +1194,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>http://www.w3.org/2000/01/rdf-schema#subClassOf n31ccfe26a08a4e0998a9be49a579bbf3b39</t>
+          <t>http://www.w3.org/2000/01/rdf-schema#subClassOf n4a1b7597cfd248eb89bbac37dd02f346b39</t>
         </is>
       </c>
     </row>
@@ -1211,7 +1211,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>http://www.w3.org/2000/01/rdf-schema#subClassOf n31ccfe26a08a4e0998a9be49a579bbf3b40</t>
+          <t>http://www.w3.org/2000/01/rdf-schema#subClassOf n4a1b7597cfd248eb89bbac37dd02f346b40</t>
         </is>
       </c>
     </row>
@@ -1228,7 +1228,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>http://www.w3.org/2000/01/rdf-schema#subClassOf n31ccfe26a08a4e0998a9be49a579bbf3b41</t>
+          <t>http://www.w3.org/2000/01/rdf-schema#subClassOf n4a1b7597cfd248eb89bbac37dd02f346b41</t>
         </is>
       </c>
     </row>
@@ -1245,7 +1245,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>http://www.w3.org/2000/01/rdf-schema#subClassOf n31ccfe26a08a4e0998a9be49a579bbf3b42</t>
+          <t>http://www.w3.org/2000/01/rdf-schema#subClassOf n4a1b7597cfd248eb89bbac37dd02f346b42</t>
         </is>
       </c>
     </row>
@@ -1262,7 +1262,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>http://www.w3.org/2000/01/rdf-schema#subClassOf n31ccfe26a08a4e0998a9be49a579bbf3b43</t>
+          <t>http://www.w3.org/2000/01/rdf-schema#subClassOf n4a1b7597cfd248eb89bbac37dd02f346b43</t>
         </is>
       </c>
     </row>
@@ -1279,7 +1279,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>http://www.w3.org/2000/01/rdf-schema#subClassOf n31ccfe26a08a4e0998a9be49a579bbf3b44</t>
+          <t>http://www.w3.org/2000/01/rdf-schema#subClassOf n4a1b7597cfd248eb89bbac37dd02f346b44</t>
         </is>
       </c>
     </row>
@@ -1373,7 +1373,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>http://www.w3.org/2000/01/rdf-schema#subClassOf n31ccfe26a08a4e0998a9be49a579bbf3b47</t>
+          <t>http://www.w3.org/2000/01/rdf-schema#subClassOf n4a1b7597cfd248eb89bbac37dd02f346b47</t>
         </is>
       </c>
     </row>
@@ -1437,7 +1437,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>http://www.w3.org/2000/01/rdf-schema#subClassOf n31ccfe26a08a4e0998a9be49a579bbf3b5</t>
+          <t>http://www.w3.org/2000/01/rdf-schema#subClassOf n4a1b7597cfd248eb89bbac37dd02f346b5</t>
         </is>
       </c>
     </row>
@@ -1454,7 +1454,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>http://www.w3.org/2000/01/rdf-schema#subClassOf n31ccfe26a08a4e0998a9be49a579bbf3b6</t>
+          <t>http://www.w3.org/2000/01/rdf-schema#subClassOf n4a1b7597cfd248eb89bbac37dd02f346b6</t>
         </is>
       </c>
     </row>
@@ -1522,7 +1522,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>http://www.w3.org/2000/01/rdf-schema#subClassOf n31ccfe26a08a4e0998a9be49a579bbf3b48</t>
+          <t>http://www.w3.org/2000/01/rdf-schema#subClassOf n4a1b7597cfd248eb89bbac37dd02f346b48</t>
         </is>
       </c>
     </row>
@@ -1556,7 +1556,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>http://www.w3.org/2000/01/rdf-schema#subClassOf n31ccfe26a08a4e0998a9be49a579bbf3b7</t>
+          <t>http://www.w3.org/2000/01/rdf-schema#subClassOf n4a1b7597cfd248eb89bbac37dd02f346b7</t>
         </is>
       </c>
     </row>
@@ -1573,7 +1573,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>http://www.w3.org/2000/01/rdf-schema#subClassOf n31ccfe26a08a4e0998a9be49a579bbf3b8</t>
+          <t>http://www.w3.org/2000/01/rdf-schema#subClassOf n4a1b7597cfd248eb89bbac37dd02f346b8</t>
         </is>
       </c>
     </row>
@@ -1590,7 +1590,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>http://www.w3.org/2000/01/rdf-schema#subClassOf n31ccfe26a08a4e0998a9be49a579bbf3b9</t>
+          <t>http://www.w3.org/2000/01/rdf-schema#subClassOf n4a1b7597cfd248eb89bbac37dd02f346b9</t>
         </is>
       </c>
     </row>
@@ -1607,7 +1607,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>http://www.w3.org/2000/01/rdf-schema#subClassOf n31ccfe26a08a4e0998a9be49a579bbf3b10</t>
+          <t>http://www.w3.org/2000/01/rdf-schema#subClassOf n4a1b7597cfd248eb89bbac37dd02f346b10</t>
         </is>
       </c>
     </row>
@@ -1624,7 +1624,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>http://www.w3.org/2000/01/rdf-schema#subClassOf n31ccfe26a08a4e0998a9be49a579bbf3b11</t>
+          <t>http://www.w3.org/2000/01/rdf-schema#subClassOf n4a1b7597cfd248eb89bbac37dd02f346b11</t>
         </is>
       </c>
     </row>
@@ -1641,7 +1641,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>http://www.w3.org/2000/01/rdf-schema#subClassOf n31ccfe26a08a4e0998a9be49a579bbf3b12</t>
+          <t>http://www.w3.org/2000/01/rdf-schema#subClassOf n4a1b7597cfd248eb89bbac37dd02f346b12</t>
         </is>
       </c>
     </row>
@@ -1658,7 +1658,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>http://www.w3.org/2000/01/rdf-schema#subClassOf n31ccfe26a08a4e0998a9be49a579bbf3b13</t>
+          <t>http://www.w3.org/2000/01/rdf-schema#subClassOf n4a1b7597cfd248eb89bbac37dd02f346b13</t>
         </is>
       </c>
     </row>
@@ -1675,7 +1675,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>http://www.w3.org/2000/01/rdf-schema#subClassOf n31ccfe26a08a4e0998a9be49a579bbf3b14</t>
+          <t>http://www.w3.org/2000/01/rdf-schema#subClassOf n4a1b7597cfd248eb89bbac37dd02f346b14</t>
         </is>
       </c>
     </row>
@@ -1709,7 +1709,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>http://www.w3.org/2000/01/rdf-schema#subClassOf n31ccfe26a08a4e0998a9be49a579bbf3b27</t>
+          <t>http://www.w3.org/2000/01/rdf-schema#subClassOf n4a1b7597cfd248eb89bbac37dd02f346b27</t>
         </is>
       </c>
     </row>
@@ -1726,7 +1726,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>http://www.w3.org/2000/01/rdf-schema#subClassOf n31ccfe26a08a4e0998a9be49a579bbf3b28</t>
+          <t>http://www.w3.org/2000/01/rdf-schema#subClassOf n4a1b7597cfd248eb89bbac37dd02f346b28</t>
         </is>
       </c>
     </row>
@@ -1743,7 +1743,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>http://www.w3.org/2000/01/rdf-schema#subClassOf n31ccfe26a08a4e0998a9be49a579bbf3b29</t>
+          <t>http://www.w3.org/2000/01/rdf-schema#subClassOf n4a1b7597cfd248eb89bbac37dd02f346b29</t>
         </is>
       </c>
     </row>
@@ -1760,7 +1760,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>http://www.w3.org/2000/01/rdf-schema#subClassOf n31ccfe26a08a4e0998a9be49a579bbf3b30</t>
+          <t>http://www.w3.org/2000/01/rdf-schema#subClassOf n4a1b7597cfd248eb89bbac37dd02f346b30</t>
         </is>
       </c>
     </row>
@@ -1777,7 +1777,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>http://www.w3.org/2000/01/rdf-schema#subClassOf n31ccfe26a08a4e0998a9be49a579bbf3b31</t>
+          <t>http://www.w3.org/2000/01/rdf-schema#subClassOf n4a1b7597cfd248eb89bbac37dd02f346b31</t>
         </is>
       </c>
     </row>
@@ -1794,7 +1794,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>http://www.w3.org/2000/01/rdf-schema#subClassOf n31ccfe26a08a4e0998a9be49a579bbf3b32</t>
+          <t>http://www.w3.org/2000/01/rdf-schema#subClassOf n4a1b7597cfd248eb89bbac37dd02f346b32</t>
         </is>
       </c>
     </row>
@@ -1811,7 +1811,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>http://www.w3.org/2000/01/rdf-schema#subClassOf n31ccfe26a08a4e0998a9be49a579bbf3b33</t>
+          <t>http://www.w3.org/2000/01/rdf-schema#subClassOf n4a1b7597cfd248eb89bbac37dd02f346b33</t>
         </is>
       </c>
     </row>
@@ -1828,7 +1828,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>http://www.w3.org/2000/01/rdf-schema#subClassOf n31ccfe26a08a4e0998a9be49a579bbf3b34</t>
+          <t>http://www.w3.org/2000/01/rdf-schema#subClassOf n4a1b7597cfd248eb89bbac37dd02f346b34</t>
         </is>
       </c>
     </row>
@@ -1862,7 +1862,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>http://www.w3.org/2000/01/rdf-schema#subClassOf n31ccfe26a08a4e0998a9be49a579bbf3b15</t>
+          <t>http://www.w3.org/2000/01/rdf-schema#subClassOf n4a1b7597cfd248eb89bbac37dd02f346b15</t>
         </is>
       </c>
     </row>
@@ -1879,7 +1879,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>http://www.w3.org/2000/01/rdf-schema#subClassOf n31ccfe26a08a4e0998a9be49a579bbf3b16</t>
+          <t>http://www.w3.org/2000/01/rdf-schema#subClassOf n4a1b7597cfd248eb89bbac37dd02f346b16</t>
         </is>
       </c>
     </row>
@@ -1896,7 +1896,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>http://www.w3.org/2000/01/rdf-schema#subClassOf n31ccfe26a08a4e0998a9be49a579bbf3b17</t>
+          <t>http://www.w3.org/2000/01/rdf-schema#subClassOf n4a1b7597cfd248eb89bbac37dd02f346b17</t>
         </is>
       </c>
     </row>
@@ -1913,7 +1913,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>http://www.w3.org/2000/01/rdf-schema#subClassOf n31ccfe26a08a4e0998a9be49a579bbf3b18</t>
+          <t>http://www.w3.org/2000/01/rdf-schema#subClassOf n4a1b7597cfd248eb89bbac37dd02f346b18</t>
         </is>
       </c>
     </row>
@@ -1930,7 +1930,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>http://www.w3.org/2000/01/rdf-schema#subClassOf n31ccfe26a08a4e0998a9be49a579bbf3b19</t>
+          <t>http://www.w3.org/2000/01/rdf-schema#subClassOf n4a1b7597cfd248eb89bbac37dd02f346b19</t>
         </is>
       </c>
     </row>
@@ -1947,7 +1947,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>http://www.w3.org/2000/01/rdf-schema#subClassOf n31ccfe26a08a4e0998a9be49a579bbf3b20</t>
+          <t>http://www.w3.org/2000/01/rdf-schema#subClassOf n4a1b7597cfd248eb89bbac37dd02f346b20</t>
         </is>
       </c>
     </row>
@@ -1964,7 +1964,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>http://www.w3.org/2000/01/rdf-schema#subClassOf n31ccfe26a08a4e0998a9be49a579bbf3b21</t>
+          <t>http://www.w3.org/2000/01/rdf-schema#subClassOf n4a1b7597cfd248eb89bbac37dd02f346b21</t>
         </is>
       </c>
     </row>
@@ -1981,7 +1981,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>http://www.w3.org/2000/01/rdf-schema#subClassOf n31ccfe26a08a4e0998a9be49a579bbf3b22</t>
+          <t>http://www.w3.org/2000/01/rdf-schema#subClassOf n4a1b7597cfd248eb89bbac37dd02f346b22</t>
         </is>
       </c>
     </row>
@@ -1998,7 +1998,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>http://www.w3.org/2000/01/rdf-schema#subClassOf n31ccfe26a08a4e0998a9be49a579bbf3b23</t>
+          <t>http://www.w3.org/2000/01/rdf-schema#subClassOf n4a1b7597cfd248eb89bbac37dd02f346b23</t>
         </is>
       </c>
     </row>
@@ -2015,7 +2015,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>http://www.w3.org/2000/01/rdf-schema#subClassOf n31ccfe26a08a4e0998a9be49a579bbf3b24</t>
+          <t>http://www.w3.org/2000/01/rdf-schema#subClassOf n4a1b7597cfd248eb89bbac37dd02f346b24</t>
         </is>
       </c>
     </row>
@@ -2032,7 +2032,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>http://www.w3.org/2000/01/rdf-schema#subClassOf n31ccfe26a08a4e0998a9be49a579bbf3b25</t>
+          <t>http://www.w3.org/2000/01/rdf-schema#subClassOf n4a1b7597cfd248eb89bbac37dd02f346b25</t>
         </is>
       </c>
     </row>
@@ -2049,7 +2049,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>http://www.w3.org/2000/01/rdf-schema#subClassOf n31ccfe26a08a4e0998a9be49a579bbf3b26</t>
+          <t>http://www.w3.org/2000/01/rdf-schema#subClassOf n4a1b7597cfd248eb89bbac37dd02f346b26</t>
         </is>
       </c>
     </row>
@@ -2083,7 +2083,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>http://www.w3.org/2000/01/rdf-schema#subClassOf n31ccfe26a08a4e0998a9be49a579bbf3b1</t>
+          <t>http://www.w3.org/2000/01/rdf-schema#subClassOf n4a1b7597cfd248eb89bbac37dd02f346b1</t>
         </is>
       </c>
     </row>
@@ -2100,7 +2100,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>http://www.w3.org/2000/01/rdf-schema#subClassOf n31ccfe26a08a4e0998a9be49a579bbf3b2</t>
+          <t>http://www.w3.org/2000/01/rdf-schema#subClassOf n4a1b7597cfd248eb89bbac37dd02f346b2</t>
         </is>
       </c>
     </row>
@@ -2117,7 +2117,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>http://www.w3.org/2000/01/rdf-schema#subClassOf n31ccfe26a08a4e0998a9be49a579bbf3b3</t>
+          <t>http://www.w3.org/2000/01/rdf-schema#subClassOf n4a1b7597cfd248eb89bbac37dd02f346b3</t>
         </is>
       </c>
     </row>
@@ -2134,7 +2134,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>http://www.w3.org/2000/01/rdf-schema#subClassOf n31ccfe26a08a4e0998a9be49a579bbf3b4</t>
+          <t>http://www.w3.org/2000/01/rdf-schema#subClassOf n4a1b7597cfd248eb89bbac37dd02f346b4</t>
         </is>
       </c>
     </row>
@@ -2313,7 +2313,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>http://www.w3.org/2000/01/rdf-schema#subClassOf n31ccfe26a08a4e0998a9be49a579bbf3b37</t>
+          <t>http://www.w3.org/2000/01/rdf-schema#subClassOf n4a1b7597cfd248eb89bbac37dd02f346b37</t>
         </is>
       </c>
     </row>
@@ -2330,7 +2330,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>http://www.w3.org/2000/01/rdf-schema#subClassOf n31ccfe26a08a4e0998a9be49a579bbf3b38</t>
+          <t>http://www.w3.org/2000/01/rdf-schema#subClassOf n4a1b7597cfd248eb89bbac37dd02f346b38</t>
         </is>
       </c>
     </row>
@@ -2347,7 +2347,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>http://www.w3.org/2000/01/rdf-schema#subClassOf n31ccfe26a08a4e0998a9be49a579bbf3b39</t>
+          <t>http://www.w3.org/2000/01/rdf-schema#subClassOf n4a1b7597cfd248eb89bbac37dd02f346b39</t>
         </is>
       </c>
     </row>
@@ -2364,7 +2364,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>http://www.w3.org/2000/01/rdf-schema#subClassOf n31ccfe26a08a4e0998a9be49a579bbf3b40</t>
+          <t>http://www.w3.org/2000/01/rdf-schema#subClassOf n4a1b7597cfd248eb89bbac37dd02f346b40</t>
         </is>
       </c>
     </row>
@@ -2381,7 +2381,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>http://www.w3.org/2000/01/rdf-schema#subClassOf n31ccfe26a08a4e0998a9be49a579bbf3b41</t>
+          <t>http://www.w3.org/2000/01/rdf-schema#subClassOf n4a1b7597cfd248eb89bbac37dd02f346b41</t>
         </is>
       </c>
     </row>
@@ -2398,7 +2398,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>http://www.w3.org/2000/01/rdf-schema#subClassOf n31ccfe26a08a4e0998a9be49a579bbf3b42</t>
+          <t>http://www.w3.org/2000/01/rdf-schema#subClassOf n4a1b7597cfd248eb89bbac37dd02f346b42</t>
         </is>
       </c>
     </row>
@@ -2415,7 +2415,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>http://www.w3.org/2000/01/rdf-schema#subClassOf n31ccfe26a08a4e0998a9be49a579bbf3b43</t>
+          <t>http://www.w3.org/2000/01/rdf-schema#subClassOf n4a1b7597cfd248eb89bbac37dd02f346b43</t>
         </is>
       </c>
     </row>
@@ -2432,7 +2432,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>http://www.w3.org/2000/01/rdf-schema#subClassOf n31ccfe26a08a4e0998a9be49a579bbf3b44</t>
+          <t>http://www.w3.org/2000/01/rdf-schema#subClassOf n4a1b7597cfd248eb89bbac37dd02f346b44</t>
         </is>
       </c>
     </row>
@@ -2466,7 +2466,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>http://www.w3.org/2000/01/rdf-schema#subClassOf n31ccfe26a08a4e0998a9be49a579bbf3b48</t>
+          <t>http://www.w3.org/2000/01/rdf-schema#subClassOf n4a1b7597cfd248eb89bbac37dd02f346b48</t>
         </is>
       </c>
     </row>
@@ -2483,7 +2483,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>http://www.w3.org/2000/01/rdf-schema#subClassOf n31ccfe26a08a4e0998a9be49a579bbf3b47</t>
+          <t>http://www.w3.org/2000/01/rdf-schema#subClassOf n4a1b7597cfd248eb89bbac37dd02f346b47</t>
         </is>
       </c>
     </row>
